--- a/05-Критерии-оценки.xlsx
+++ b/05-Критерии-оценки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krivonosova.nv\Desktop\Профессионалы_2026\ПРдБ_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Чемпионат ГЭ\2026\Основная\ККД_ПРдБ_2026_основная\ККД_ПРдБ_2026_основная\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943715AA-A7BA-4E12-82B1-631718FDE427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA3BBF8-503C-4840-B8D0-719D1240CD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,20 @@
     <sheet name="Перечень профессиональных задач" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/05-Критерии-оценки.xlsx
+++ b/05-Критерии-оценки.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Чемпионат ГЭ\2026\Основная\ККД_ПРдБ_2026_основная\ККД_ПРдБ_2026_основная\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vadim\Desktop\VendingSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA3BBF8-503C-4840-B8D0-719D1240CD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0567D67-4C4C-4EBC-AAF1-6C6AAF33EF79}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Критерии оценки" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -1534,7 +1531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1919,6 +1916,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6317,6 +6315,10 @@
       <c r="I214" s="48">
         <v>0.4</v>
       </c>
+      <c r="J214" s="132"/>
+      <c r="K214" s="132"/>
+      <c r="L214" s="132"/>
+      <c r="M214" s="132"/>
     </row>
     <row r="215" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A215" s="55"/>

--- a/05-Критерии-оценки.xlsx
+++ b/05-Критерии-оценки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vadim\Desktop\VendingSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0567D67-4C4C-4EBC-AAF1-6C6AAF33EF79}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAB19E1-583A-4C6E-926F-7DA0A045D97C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="382">
   <si>
     <t>Мероприятие</t>
   </si>
@@ -1154,6 +1154,72 @@
   </si>
   <si>
     <t>Перечень профессиональных задач соответствует таблице 1 Конкурсного задания</t>
+  </si>
+  <si>
+    <t>Диаграммы</t>
+  </si>
+  <si>
+    <t>UseCase</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>IDEF0</t>
+  </si>
+  <si>
+    <t>WireFrame</t>
+  </si>
+  <si>
+    <t>Приложения</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Уведомления</t>
+  </si>
+  <si>
+    <t>Web ТА</t>
+  </si>
+  <si>
+    <t>Web Календарь</t>
+  </si>
+  <si>
+    <t>Web График</t>
+  </si>
+  <si>
+    <t>База данных</t>
+  </si>
+  <si>
+    <t>Бд</t>
+  </si>
+  <si>
+    <t>Импорт</t>
+  </si>
+  <si>
+    <t>Ограничения</t>
+  </si>
+  <si>
+    <t>Postman</t>
+  </si>
+  <si>
+    <t>Тестирование</t>
+  </si>
+  <si>
+    <t>Ручное</t>
+  </si>
+  <si>
+    <t>Автомат</t>
+  </si>
+  <si>
+    <t>Охрана труда</t>
+  </si>
+  <si>
+    <t>Презентация</t>
   </si>
 </sst>
 </file>
@@ -1897,6 +1963,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1916,7 +1983,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2159,7 +2225,9 @@
     <col min="7" max="7" width="26.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="7.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="7.625" style="50" customWidth="1"/>
-    <col min="10" max="26" width="8.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="26" width="8.5" style="1" customWidth="1"/>
     <col min="27" max="16384" width="11.125" style="1"/>
   </cols>
   <sheetData>
@@ -2245,15 +2313,15 @@
       <c r="A6" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
-      <c r="E6" s="126"/>
-      <c r="F6" s="126"/>
-      <c r="G6" s="126"/>
-      <c r="H6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="128"/>
       <c r="I6" s="54">
         <f>SUM(I7:I54)</f>
         <v>18.199999999999982</v>
@@ -3206,15 +3274,15 @@
       <c r="A55" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="128" t="s">
+      <c r="B55" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="129"/>
-      <c r="D55" s="129"/>
-      <c r="E55" s="129"/>
-      <c r="F55" s="129"/>
-      <c r="G55" s="129"/>
-      <c r="H55" s="129"/>
+      <c r="C55" s="130"/>
+      <c r="D55" s="130"/>
+      <c r="E55" s="130"/>
+      <c r="F55" s="130"/>
+      <c r="G55" s="130"/>
+      <c r="H55" s="130"/>
       <c r="I55" s="54">
         <f>SUM(I56:I219)</f>
         <v>69.400000000000063</v>
@@ -3712,7 +3780,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A81" s="55"/>
       <c r="B81" s="11"/>
       <c r="C81" s="57" t="s">
@@ -3733,7 +3801,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A82" s="55"/>
       <c r="B82" s="11"/>
       <c r="C82" s="57" t="s">
@@ -3752,7 +3820,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A83" s="55"/>
       <c r="B83" s="11"/>
       <c r="C83" s="57" t="s">
@@ -3773,7 +3841,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A84" s="55"/>
       <c r="B84" s="11"/>
       <c r="C84" s="57" t="s">
@@ -3794,7 +3862,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A85" s="55"/>
       <c r="B85" s="11"/>
       <c r="C85" s="57" t="s">
@@ -3815,7 +3883,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="55"/>
       <c r="B86" s="11"/>
       <c r="C86" s="57" t="s">
@@ -3836,7 +3904,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="55"/>
       <c r="B87" s="11"/>
       <c r="C87" s="57" t="s">
@@ -3855,7 +3923,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A88" s="55"/>
       <c r="B88" s="11"/>
       <c r="C88" s="57" t="s">
@@ -3876,7 +3944,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A89" s="55"/>
       <c r="B89" s="11"/>
       <c r="C89" s="57" t="s">
@@ -3895,7 +3963,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A90" s="55"/>
       <c r="B90" s="11"/>
       <c r="C90" s="57" t="s">
@@ -3914,7 +3982,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A91" s="55"/>
       <c r="B91" s="11"/>
       <c r="C91" s="57" t="s">
@@ -3935,7 +4003,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="55"/>
       <c r="B92" s="11"/>
       <c r="C92" s="57" t="s">
@@ -3954,7 +4022,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A93" s="55"/>
       <c r="B93" s="11"/>
       <c r="C93" s="57" t="s">
@@ -3973,7 +4041,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A94" s="55"/>
       <c r="B94" s="11"/>
       <c r="C94" s="57" t="s">
@@ -3992,7 +4060,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A95" s="55"/>
       <c r="B95" s="11"/>
       <c r="C95" s="57" t="s">
@@ -4010,8 +4078,9 @@
       <c r="I95" s="36">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="P95" s="125"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="55"/>
       <c r="B96" s="11"/>
       <c r="C96" s="57" t="s">
@@ -4029,6 +4098,7 @@
       <c r="I96" s="36">
         <v>0.3</v>
       </c>
+      <c r="P96" s="125"/>
     </row>
     <row r="97" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A97" s="55"/>
@@ -4182,7 +4252,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A105" s="55"/>
       <c r="B105" s="11"/>
       <c r="C105" s="57" t="s">
@@ -6315,10 +6385,10 @@
       <c r="I214" s="48">
         <v>0.4</v>
       </c>
-      <c r="J214" s="132"/>
-      <c r="K214" s="132"/>
-      <c r="L214" s="132"/>
-      <c r="M214" s="132"/>
+      <c r="J214" s="125"/>
+      <c r="K214" s="125"/>
+      <c r="L214" s="125"/>
+      <c r="M214" s="125"/>
     </row>
     <row r="215" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A215" s="55"/>
@@ -6415,15 +6485,15 @@
       <c r="A220" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="B220" s="128" t="s">
+      <c r="B220" s="129" t="s">
         <v>269</v>
       </c>
-      <c r="C220" s="129"/>
-      <c r="D220" s="129"/>
-      <c r="E220" s="129"/>
-      <c r="F220" s="129"/>
-      <c r="G220" s="129"/>
-      <c r="H220" s="129"/>
+      <c r="C220" s="130"/>
+      <c r="D220" s="130"/>
+      <c r="E220" s="130"/>
+      <c r="F220" s="130"/>
+      <c r="G220" s="130"/>
+      <c r="H220" s="130"/>
       <c r="I220" s="54">
         <f>SUM(I221:I230)</f>
         <v>4.5</v>
@@ -6648,15 +6718,15 @@
       <c r="A231" s="53" t="s">
         <v>282</v>
       </c>
-      <c r="B231" s="128" t="s">
+      <c r="B231" s="129" t="s">
         <v>283</v>
       </c>
-      <c r="C231" s="129"/>
-      <c r="D231" s="129"/>
-      <c r="E231" s="129"/>
-      <c r="F231" s="129"/>
-      <c r="G231" s="129"/>
-      <c r="H231" s="129"/>
+      <c r="C231" s="130"/>
+      <c r="D231" s="130"/>
+      <c r="E231" s="130"/>
+      <c r="F231" s="130"/>
+      <c r="G231" s="130"/>
+      <c r="H231" s="130"/>
       <c r="I231" s="54">
         <f>SUM(I232:I267)</f>
         <v>7.9</v>
@@ -7142,7 +7212,7 @@
       <c r="H256" s="114"/>
       <c r="I256" s="117"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="110"/>
       <c r="B257" s="112"/>
       <c r="C257" s="110" t="s">
@@ -7161,7 +7231,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="110"/>
       <c r="B258" s="113"/>
       <c r="C258" s="110"/>
@@ -7176,7 +7246,7 @@
       <c r="H258" s="114"/>
       <c r="I258" s="115"/>
     </row>
-    <row r="259" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A259" s="110"/>
       <c r="B259" s="112"/>
       <c r="C259" s="110"/>
@@ -7191,7 +7261,7 @@
       <c r="H259" s="114"/>
       <c r="I259" s="115"/>
     </row>
-    <row r="260" spans="1:9" ht="39" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" ht="39" x14ac:dyDescent="0.25">
       <c r="A260" s="112"/>
       <c r="B260" s="112"/>
       <c r="C260" s="110"/>
@@ -7206,7 +7276,7 @@
       <c r="H260" s="114"/>
       <c r="I260" s="117"/>
     </row>
-    <row r="261" spans="1:9" ht="39" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" ht="39" x14ac:dyDescent="0.25">
       <c r="A261" s="112"/>
       <c r="B261" s="112"/>
       <c r="C261" s="110"/>
@@ -7221,7 +7291,7 @@
       <c r="H261" s="114"/>
       <c r="I261" s="117"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" s="118">
         <v>6</v>
       </c>
@@ -7236,7 +7306,7 @@
       <c r="H262" s="120"/>
       <c r="I262" s="121"/>
     </row>
-    <row r="263" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A263" s="122"/>
       <c r="B263" s="119"/>
       <c r="C263" s="120" t="s">
@@ -7255,7 +7325,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A264" s="122"/>
       <c r="B264" s="119"/>
       <c r="C264" s="120" t="s">
@@ -7274,7 +7344,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A265" s="122"/>
       <c r="B265" s="119"/>
       <c r="C265" s="120" t="s">
@@ -7293,7 +7363,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A266" s="122"/>
       <c r="B266" s="119"/>
       <c r="C266" s="120" t="s">
@@ -7312,7 +7382,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A267" s="122"/>
       <c r="B267" s="119"/>
       <c r="C267" s="120" t="s">
@@ -7331,7 +7401,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" s="55"/>
       <c r="B268" s="106"/>
       <c r="C268" s="3"/>
@@ -7340,7 +7410,7 @@
       <c r="F268" s="109"/>
       <c r="G268" s="27"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" s="82"/>
       <c r="B269" s="42"/>
       <c r="C269" s="83"/>
@@ -7356,177 +7426,335 @@
         <v>100.00000000000006</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="49"/>
       <c r="C270" s="46"/>
       <c r="E270" s="46"/>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K270" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="49"/>
       <c r="C271" s="46"/>
       <c r="E271" s="46"/>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K271" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="L271" s="125">
+        <f>SUM(I8:I12)</f>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" s="49"/>
       <c r="C272" s="46"/>
       <c r="E272" s="46"/>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K272" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="L272" s="125">
+        <f>SUM(I14:I19)</f>
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="49"/>
       <c r="C273" s="46"/>
       <c r="E273" s="46"/>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K273" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="L273" s="125">
+        <f>SUM(I21:I25)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="49"/>
       <c r="C274" s="46"/>
       <c r="E274" s="46"/>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K274" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="L274" s="125">
+        <f>SUM(I27:I54)</f>
+        <v>5.6000000000000023</v>
+      </c>
+      <c r="M274" s="125">
+        <f>SUM(L271:L274)</f>
+        <v>18.200000000000003</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="49"/>
       <c r="C275" s="46"/>
       <c r="E275" s="46"/>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="49"/>
       <c r="C276" s="46"/>
       <c r="E276" s="46"/>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K276" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" s="49"/>
       <c r="C277" s="46"/>
       <c r="E277" s="46"/>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K277" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="L277" s="125">
+        <f>SUM(I171:I184)</f>
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" s="49"/>
       <c r="C278" s="46"/>
       <c r="E278" s="46"/>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K278" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="L278" s="125">
+        <f>SUM(I186:I190)</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" s="49"/>
       <c r="C279" s="46"/>
       <c r="E279" s="46"/>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K279" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="L279" s="1">
+        <f>SUM(I192:I202)</f>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="M279" s="125">
+        <f>SUM(L277:L279)</f>
+        <v>13.700000000000001</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" s="49"/>
       <c r="C280" s="46"/>
       <c r="E280" s="46"/>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" s="49"/>
       <c r="C281" s="46"/>
       <c r="E281" s="46"/>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K281" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" s="49"/>
       <c r="C282" s="46"/>
       <c r="E282" s="46"/>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K282" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="L282" s="125">
+        <f>SUM(I57:I120)</f>
+        <v>29.000000000000014</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" s="49"/>
       <c r="C283" s="46"/>
       <c r="E283" s="46"/>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K283" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="L283" s="125">
+        <f>SUM(I122:I131)</f>
+        <v>3.1</v>
+      </c>
+      <c r="M283" s="125">
+        <f>SUM(L282:L283)</f>
+        <v>32.100000000000016</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" s="49"/>
       <c r="C284" s="46"/>
       <c r="E284" s="46"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" s="49"/>
       <c r="C285" s="46"/>
       <c r="E285" s="46"/>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K285" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L285" s="125">
+        <f>SUM(I133:I142)</f>
+        <v>3.3000000000000007</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" s="49"/>
       <c r="C286" s="46"/>
       <c r="E286" s="46"/>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K286" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="L286" s="125">
+        <f>SUM(I144:I151)</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" s="49"/>
       <c r="C287" s="46"/>
       <c r="E287" s="46"/>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K287" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="L287" s="125">
+        <f>SUM(I153:I169)</f>
+        <v>7.6000000000000005</v>
+      </c>
+      <c r="M287" s="125">
+        <f>SUM(L285:L287)</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" s="49"/>
       <c r="C288" s="46"/>
       <c r="E288" s="46"/>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" s="49"/>
       <c r="C289" s="46"/>
       <c r="E289" s="46"/>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K289" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="L289" s="125">
+        <f>SUM(I204:I218)</f>
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" s="49"/>
       <c r="C290" s="46"/>
       <c r="E290" s="46"/>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" s="49"/>
       <c r="C291" s="46"/>
       <c r="E291" s="46"/>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K291" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="L291" s="125">
+        <f>SUM(I233:I243)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" s="49"/>
       <c r="C292" s="46"/>
       <c r="E292" s="46"/>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" s="49"/>
       <c r="C293" s="46"/>
       <c r="E293" s="46"/>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K293" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" s="49"/>
       <c r="C294" s="46"/>
       <c r="E294" s="46"/>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K294" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="L294" s="125">
+        <f>SUM(I222:I224)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" s="49"/>
       <c r="C295" s="46"/>
       <c r="E295" s="46"/>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K295" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="L295" s="125">
+        <f>SUM(I226:I230)</f>
+        <v>2.5</v>
+      </c>
+      <c r="M295" s="125">
+        <f>SUM(L294:L295)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" s="49"/>
       <c r="C296" s="46"/>
       <c r="E296" s="46"/>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="49"/>
       <c r="C297" s="46"/>
       <c r="E297" s="46"/>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K297" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="L297" s="125">
+        <f>SUM(I245:I257)</f>
+        <v>2.8999999999999995</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="49"/>
       <c r="C298" s="46"/>
       <c r="E298" s="46"/>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" s="49"/>
       <c r="C299" s="46"/>
       <c r="E299" s="46"/>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K299" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="L299" s="125">
+        <f>SUM(I263:I267)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" s="49"/>
       <c r="C300" s="46"/>
       <c r="E300" s="46"/>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" s="49"/>
       <c r="C301" s="46"/>
       <c r="E301" s="46"/>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" s="49"/>
       <c r="C302" s="46"/>
       <c r="E302" s="46"/>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" s="49"/>
       <c r="C303" s="46"/>
       <c r="E303" s="46"/>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" s="49"/>
       <c r="C304" s="46"/>
       <c r="E304" s="46"/>
@@ -10360,10 +10588,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="131" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="131"/>
+      <c r="B1" s="132"/>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45">
